--- a/results/Int Task Remove ACC -0.2/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_1_permute.xlsx
@@ -440,147 +440,147 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6957344053529031</v>
+        <v>0.7002902315685609</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6953624618420646</v>
+        <v>0.7005392217322932</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6946856402824457</v>
+        <v>0.6985503838919552</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6983106441367827</v>
+        <v>0.6945981468348186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7015941537417902</v>
+        <v>0.6984944960069069</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6957902932379514</v>
+        <v>0.6984944960069069</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.69679434800037</v>
+        <v>0.6973755820048719</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6912090283987542</v>
+        <v>0.7154528074989979</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6752466775615923</v>
+        <v>0.7150920415651691</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6825494896857944</v>
+        <v>0.706952838333693</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6756745089574789</v>
+        <v>0.7090646295211371</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.672306589374364</v>
+        <v>0.6991744010360457</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6683400912706978</v>
+        <v>0.6984975794764269</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6674254571243563</v>
+        <v>0.6816460331164627</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.642176466960624</v>
+        <v>0.6913655144768893</v>
       </c>
     </row>
     <row r="17">
@@ -590,627 +590,627 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6437008572045265</v>
+        <v>0.6916815701026795</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6633136505195647</v>
+        <v>0.6954996762357004</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6739874656964016</v>
+        <v>0.694391939810675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6739011285498442</v>
+        <v>0.6972029077117572</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6796795504301441</v>
+        <v>0.6760849958373162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6616104190435077</v>
+        <v>0.6675514939409823</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6753014091455707</v>
+        <v>0.6432394930776109</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6667363016866579</v>
+        <v>0.6436114365884493</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6688257377200826</v>
+        <v>0.6344323332613857</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6632038019179181</v>
+        <v>0.6299262279917364</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6628318584070796</v>
+        <v>0.6300156486078136</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6278144368042922</v>
+        <v>0.6246091702383522</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6275704572785298</v>
+        <v>0.6046660602509945</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6290135210138448</v>
+        <v>0.5999221423946224</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6215399617649779</v>
+        <v>0.5993794517591193</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6215399617649779</v>
+        <v>0.6015583084086213</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6389210940149856</v>
+        <v>0.5995390213067744</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6194443587925134</v>
+        <v>0.5762757855138602</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6082532916037126</v>
+        <v>0.5762757855138602</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.608558169652493</v>
+        <v>0.5655907927600136</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6075174986895254</v>
+        <v>0.5653803459652802</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6050561191452623</v>
+        <v>0.5653803459652802</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6036099719404273</v>
+        <v>0.5699118898584687</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5767329098701859</v>
+        <v>0.5644129074034103</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5682776510129197</v>
+        <v>0.5576782245382504</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5676343621843298</v>
+        <v>0.5538813172581789</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5429747001325892</v>
+        <v>0.5548071289815301</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5429747001325892</v>
+        <v>0.5532715611606179</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5434838580370633</v>
+        <v>0.559777681847615</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5426362893527797</v>
+        <v>0.5595541303074218</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5471759273534581</v>
+        <v>0.5574758718510068</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5479564305756838</v>
+        <v>0.5708723906139188</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.538910687305356</v>
+        <v>0.550481406678795</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5360661866732448</v>
+        <v>0.5480312047115414</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5376017544941568</v>
+        <v>0.5358276032191422</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5375793993401375</v>
+        <v>0.542598902284851</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.538010314205544</v>
+        <v>0.541250269803583</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.538010314205544</v>
+        <v>0.5250277512256791</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.539036724121982</v>
+        <v>0.5225104837963677</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5207868243347414</v>
+        <v>0.4929554284480898</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5207868243347414</v>
+        <v>0.5058944374209861</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4895011717184176</v>
+        <v>0.5081993308871142</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.504325336869045</v>
+        <v>0.5081993308871142</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5055895593722056</v>
+        <v>0.5112878110449879</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5034554130307421</v>
+        <v>0.5199727883814869</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5028456569331812</v>
+        <v>0.5314097622645</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4958477228577595</v>
+        <v>0.5314097622645</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4742827079029324</v>
+        <v>0.5313985846874903</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4649158983688447</v>
+        <v>0.5186129783232093</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4649158983688447</v>
+        <v>0.5105651228762603</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4648935432148253</v>
+        <v>0.5105651228762603</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4986047300422435</v>
+        <v>0.4991890475162653</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4986047300422435</v>
+        <v>0.5011077364250254</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5052418981838365</v>
+        <v>0.5008475686842835</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5064837655329777</v>
+        <v>0.5011748018870833</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5040925349202923</v>
+        <v>0.497980712898153</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5049959914896242</v>
+        <v>0.5026097715149086</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5026433042459375</v>
+        <v>0.5047215627023527</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5023160710431377</v>
+        <v>0.5018069131386635</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5048109833184299</v>
+        <v>0.5018069131386635</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5005650457895223</v>
+        <v>0.5030264253337855</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5008699238383029</v>
+        <v>0.5014908575128735</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4996504116431809</v>
+        <v>0.5026991921309858</v>
       </c>
     </row>
     <row r="80">
@@ -1220,107 +1220,107 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4996504116431809</v>
+        <v>0.5036138262773272</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4993343560173908</v>
+        <v>0.5023943140822053</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5002937004717708</v>
+        <v>0.5023943140822053</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5002937004717708</v>
+        <v>0.5023943140822053</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4999776448459807</v>
+        <v>0.5021006136104345</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4999776448459807</v>
+        <v>0.5029705374487373</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4999888224229904</v>
+        <v>0.5038963491720884</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5002937004717708</v>
+        <v>0.5038739940180691</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.500609756097561</v>
+        <v>0.504134161758811</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.500609756097561</v>
+        <v>0.5003638494033487</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.500609756097561</v>
+        <v>0.5010183158089482</v>
       </c>
     </row>
   </sheetData>
